--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,48 +922,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90569592</v>
+        <v>136531725</v>
       </c>
       <c r="B4" t="n">
-        <v>109815</v>
+        <v>43280</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220204</v>
+        <v>101248</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Husås – Andviken – väg Z751, Jmt</t>
+          <t>Z751 Lit, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487767</v>
+        <v>487764</v>
       </c>
       <c r="R4" t="n">
-        <v>7040361</v>
+        <v>7040223</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,17 +987,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-07-12</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-07-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Allmän</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,31 +1003,1096 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136531725</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136532069</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43280</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101248</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Violett guldvinge</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycaena helle</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Z751 Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>487789</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7040106</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136532069</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136532868</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43280</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101248</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Violett guldvinge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycaena helle</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Z751 Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>487777</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7040361</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136532868</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136534639</v>
+      </c>
+      <c r="B7" t="n">
+        <v>43280</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>101248</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Violett guldvinge</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycaena helle</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Z751 Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>487778</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7040079</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136534639</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136534780</v>
+      </c>
+      <c r="B8" t="n">
+        <v>43280</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>101248</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Violett guldvinge</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycaena helle</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Z751 Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>487778</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7040118</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136534780</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136537217</v>
+      </c>
+      <c r="B9" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Z751 Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>487775</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7040353</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136537217</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>90569592</v>
+      </c>
+      <c r="B10" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Husås – Andviken – väg Z751, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>487767</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7040361</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-07-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-07-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Allmän</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Leif Andersson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Emma Karlsson, Therese Kalling</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/90569592</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136530749</v>
+      </c>
+      <c r="B11" t="n">
+        <v>110059</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Z751 Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>487780</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7040381</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136530749</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136534634</v>
+      </c>
+      <c r="B12" t="n">
+        <v>110059</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Z751 Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>487780</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7040126</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136534634</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136534999</v>
+      </c>
+      <c r="B13" t="n">
+        <v>110059</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Z751 Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>487781</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7040368</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136534999</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136552562</v>
+      </c>
+      <c r="B14" t="n">
+        <v>110059</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Z751 Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>487792</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7040122</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136552562</t>
         </is>
       </c>
     </row>
@@ -1041,6 +2101,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>136537217</v>
       </c>
       <c r="B9" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>136530749</v>
       </c>
       <c r="B11" t="n">
-        <v>110059</v>
+        <v>110062</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136534634</v>
       </c>
       <c r="B12" t="n">
-        <v>110059</v>
+        <v>110062</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136534999</v>
       </c>
       <c r="B13" t="n">
-        <v>110059</v>
+        <v>110062</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136552562</v>
       </c>
       <c r="B14" t="n">
-        <v>110059</v>
+        <v>110062</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>136537217</v>
       </c>
       <c r="B9" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>136530749</v>
       </c>
       <c r="B11" t="n">
-        <v>110062</v>
+        <v>110063</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136534634</v>
       </c>
       <c r="B12" t="n">
-        <v>110062</v>
+        <v>110063</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136534999</v>
       </c>
       <c r="B13" t="n">
-        <v>110062</v>
+        <v>110063</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136552562</v>
       </c>
       <c r="B14" t="n">
-        <v>110062</v>
+        <v>110063</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136531725</v>
       </c>
       <c r="B4" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136532069</v>
       </c>
       <c r="B5" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136532868</v>
       </c>
       <c r="B6" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136534639</v>
       </c>
       <c r="B7" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136534780</v>
       </c>
       <c r="B8" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>136537217</v>
       </c>
       <c r="B9" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>136530749</v>
       </c>
       <c r="B11" t="n">
-        <v>110063</v>
+        <v>110068</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136534634</v>
       </c>
       <c r="B12" t="n">
-        <v>110063</v>
+        <v>110068</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136534999</v>
       </c>
       <c r="B13" t="n">
-        <v>110063</v>
+        <v>110068</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136552562</v>
       </c>
       <c r="B14" t="n">
-        <v>110063</v>
+        <v>110068</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>136537217</v>
       </c>
       <c r="B9" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>136530749</v>
       </c>
       <c r="B11" t="n">
-        <v>110068</v>
+        <v>110070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136534634</v>
       </c>
       <c r="B12" t="n">
-        <v>110068</v>
+        <v>110070</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136534999</v>
       </c>
       <c r="B13" t="n">
-        <v>110068</v>
+        <v>110070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136552562</v>
       </c>
       <c r="B14" t="n">
-        <v>110068</v>
+        <v>110070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2093,6 +2093,1767 @@
       <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136552562</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136951461</v>
+      </c>
+      <c r="B15" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>487772</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7040322</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136951461</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136951462</v>
+      </c>
+      <c r="B16" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>487779</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7040349</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136951462</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136951463</v>
+      </c>
+      <c r="B17" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>487781</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7040382</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136951463</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136955317</v>
+      </c>
+      <c r="B18" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>487763</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7040268</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136955317</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136955319</v>
+      </c>
+      <c r="B19" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>487765</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7040288</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136955319</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136955321</v>
+      </c>
+      <c r="B20" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>487776</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7040297</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136955321</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136955323</v>
+      </c>
+      <c r="B21" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>487779</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7040308</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136955323</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136955325</v>
+      </c>
+      <c r="B22" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>487765</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7040305</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136955325</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136955327</v>
+      </c>
+      <c r="B23" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>487765</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7040314</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136955327</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136955329</v>
+      </c>
+      <c r="B24" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>487765</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7040330</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136955329</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136955333</v>
+      </c>
+      <c r="B25" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>487768</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7040340</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136955333</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136955335</v>
+      </c>
+      <c r="B26" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>487784</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7040359</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136955335</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136955337</v>
+      </c>
+      <c r="B27" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>487771</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7040353</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136955337</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136955339</v>
+      </c>
+      <c r="B28" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>487775</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7040364</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136955339</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136955341</v>
+      </c>
+      <c r="B29" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>487776</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7040372</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136955341</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136955343</v>
+      </c>
+      <c r="B30" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>487777</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7040385</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136955343</t>
         </is>
       </c>
     </row>
@@ -2111,6 +3872,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>136537217</v>
       </c>
       <c r="B9" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>136530749</v>
       </c>
       <c r="B11" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136534634</v>
       </c>
       <c r="B12" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136534999</v>
       </c>
       <c r="B13" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136552562</v>
       </c>
       <c r="B14" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>136537217</v>
       </c>
       <c r="B9" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>136530749</v>
       </c>
       <c r="B11" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136534634</v>
       </c>
       <c r="B12" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136534999</v>
       </c>
       <c r="B13" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136552562</v>
       </c>
       <c r="B14" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>136537217</v>
       </c>
       <c r="B9" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>136530749</v>
       </c>
       <c r="B11" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136534634</v>
       </c>
       <c r="B12" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136534999</v>
       </c>
       <c r="B13" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136552562</v>
       </c>
       <c r="B14" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>136537217</v>
       </c>
       <c r="B9" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>136530749</v>
       </c>
       <c r="B11" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136534634</v>
       </c>
       <c r="B12" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136534999</v>
       </c>
       <c r="B13" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136552562</v>
       </c>
       <c r="B14" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>136537217</v>
       </c>
       <c r="B9" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>136530749</v>
       </c>
       <c r="B11" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136534634</v>
       </c>
       <c r="B12" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136534999</v>
       </c>
       <c r="B13" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136552562</v>
       </c>
       <c r="B14" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -1764,7 +1764,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist</t>
+          <t>Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>136537217</v>
       </c>
       <c r="B9" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>136530749</v>
       </c>
       <c r="B11" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1783,7 +1783,7 @@
         <v>136534634</v>
       </c>
       <c r="B12" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136534999</v>
       </c>
       <c r="B13" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136552562</v>
       </c>
       <c r="B14" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>136537217</v>
       </c>
       <c r="B9" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>136530749</v>
       </c>
       <c r="B11" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136534634</v>
       </c>
       <c r="B12" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136534999</v>
       </c>
       <c r="B13" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136552562</v>
       </c>
       <c r="B14" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136531725</v>
       </c>
       <c r="B4" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136532069</v>
       </c>
       <c r="B5" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136532868</v>
       </c>
       <c r="B6" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136534639</v>
       </c>
       <c r="B7" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136534780</v>
       </c>
       <c r="B8" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>136537217</v>
       </c>
       <c r="B9" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>136530749</v>
       </c>
       <c r="B11" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136534634</v>
       </c>
       <c r="B12" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136534999</v>
       </c>
       <c r="B13" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136552562</v>
       </c>
       <c r="B14" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist</t>
+          <t>Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136531725</v>
       </c>
       <c r="B4" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136532069</v>
       </c>
       <c r="B5" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136532868</v>
       </c>
       <c r="B6" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136534639</v>
       </c>
       <c r="B7" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136534780</v>
       </c>
       <c r="B8" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>136537217</v>
       </c>
       <c r="B9" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>136530749</v>
       </c>
       <c r="B11" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136534634</v>
       </c>
       <c r="B12" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136534999</v>
       </c>
       <c r="B13" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136552562</v>
       </c>
       <c r="B14" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 13898-2026 artfynd.xlsx
+++ b/artfynd/A 13898-2026 artfynd.xlsx
@@ -2101,7 +2101,7 @@
         <v>136951461</v>
       </c>
       <c r="B15" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136951462</v>
       </c>
       <c r="B16" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136951463</v>
       </c>
       <c r="B17" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136955317</v>
       </c>
       <c r="B18" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136955319</v>
       </c>
       <c r="B19" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136955321</v>
       </c>
       <c r="B20" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136955323</v>
       </c>
       <c r="B21" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136955325</v>
       </c>
       <c r="B22" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>136955327</v>
       </c>
       <c r="B23" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136955329</v>
       </c>
       <c r="B24" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>136955333</v>
       </c>
       <c r="B25" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136955335</v>
       </c>
       <c r="B26" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>136955337</v>
       </c>
       <c r="B27" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136955339</v>
       </c>
       <c r="B28" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136955341</v>
       </c>
       <c r="B29" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136955343</v>
       </c>
       <c r="B30" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
